--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,31 +425,31 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2676"/>
+  <dimension ref="A1:E2677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>sorteo</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>primero</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>segundo</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>tercero</t>
         </is>
@@ -72665,6 +72677,33 @@
       <c r="E2676" t="inlineStr">
         <is>
           <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="2677">
+      <c r="A2677" t="inlineStr">
+        <is>
+          <t>2026-09-16</t>
+        </is>
+      </c>
+      <c r="B2677" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2677" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D2677" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="E2677" t="inlineStr">
+        <is>
+          <t>35</t>
         </is>
       </c>
     </row>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2727"/>
+  <dimension ref="A1:E2728"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74057,6 +74057,33 @@
         </is>
       </c>
     </row>
+    <row r="2728">
+      <c r="A2728" t="inlineStr">
+        <is>
+          <t>2026-10-11</t>
+        </is>
+      </c>
+      <c r="B2728" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2728" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="D2728" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2728" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/histories/La suerte history.xlsx
+++ b/data/histories/La suerte history.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E2750"/>
+  <dimension ref="A1:E2754"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -74678,6 +74678,114 @@
         </is>
       </c>
     </row>
+    <row r="2751">
+      <c r="A2751" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2751" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2751" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="D2751" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="E2751" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+    </row>
+    <row r="2752">
+      <c r="A2752" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2752" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2752" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="D2752" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E2752" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+    </row>
+    <row r="2753">
+      <c r="A2753" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2753" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte</t>
+        </is>
+      </c>
+      <c r="C2753" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D2753" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="E2753" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+    </row>
+    <row r="2754">
+      <c r="A2754" t="inlineStr">
+        <is>
+          <t>2026-10-24</t>
+        </is>
+      </c>
+      <c r="B2754" t="inlineStr">
+        <is>
+          <t>Quiniela La Suerte 6PM</t>
+        </is>
+      </c>
+      <c r="C2754" t="inlineStr">
+        <is>
+          <t>09</t>
+        </is>
+      </c>
+      <c r="D2754" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E2754" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
